--- a/Heuer_etal_2019/Heuer_etal_2019_Table1_snapshot.xlsx
+++ b/Heuer_etal_2019/Heuer_etal_2019_Table1_snapshot.xlsx
@@ -1719,13 +1719,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D1889ED-14F6-4C2A-86C6-3A3A7265280E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A596499-75BF-4DF1-B14E-3D0317866D44}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A3E9F3-A82D-4E51-93C7-C6E24EE11732}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A6E0443-EF22-4BAA-B7D4-C8D413E0525D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CA2055B-3E91-4CF0-9159-ED7F87F2B9A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1E51CCB-B900-45A0-8FFD-C3B9093FFE63}"/>
 </file>
--- a/Heuer_etal_2019/Heuer_etal_2019_Table1_snapshot.xlsx
+++ b/Heuer_etal_2019/Heuer_etal_2019_Table1_snapshot.xlsx
@@ -1719,13 +1719,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A596499-75BF-4DF1-B14E-3D0317866D44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE15827-7B6F-4C76-ABCC-432065D18347}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A6E0443-EF22-4BAA-B7D4-C8D413E0525D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{764681F0-C04C-4F48-947E-28F18995E25C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1E51CCB-B900-45A0-8FFD-C3B9093FFE63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A345A819-D26C-4856-8C16-018FBA93454A}"/>
 </file>